--- a/output/pdf_financials_xlsx/CRR.UN.xlsx
+++ b/output/pdf_financials_xlsx/CRR.UN.xlsx
@@ -61238,7 +61238,7 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E569" s="5" t="n">

--- a/output/pdf_financials_xlsx/CRR.UN.xlsx
+++ b/output/pdf_financials_xlsx/CRR.UN.xlsx
@@ -2173,34 +2173,34 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>22.971</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>21.944</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>16.939</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>5.026</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>5.888</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>7.383</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>5.606</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>6.654</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>-96.35299999999999</v>
@@ -2230,34 +2230,34 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>14.588</v>
+        <v>37.559</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>10.748</v>
+        <v>32.692</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>14.663</v>
+        <v>31.602</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>37.915</v>
+        <v>42.941</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>39.835</v>
+        <v>45.723</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>34.877</v>
+        <v>42.26</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>68.964</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>64.465</v>
+        <v>69.94499999999999</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>126.356</v>
+        <v>132.526</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>86.218</v>
+        <v>92.872</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>11.057</v>
@@ -2287,13 +2287,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>7.74951658485795</v>
+        <v>19.95229595631202</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>5.170688527113882</v>
+        <v>15.72759111726898</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>6.746479067648832</v>
+        <v>14.54015082151254</v>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
@@ -46918,7 +46918,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -46962,10 +46962,10 @@
         </is>
       </c>
       <c r="M414" s="5" t="n">
-        <v>-6.17</v>
+        <v>6.17</v>
       </c>
       <c r="N414" s="5" t="n">
-        <v>-6.654</v>
+        <v>6.654</v>
       </c>
       <c r="O414" t="inlineStr">
         <is>
@@ -49920,7 +49920,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
@@ -49949,13 +49949,13 @@
         </is>
       </c>
       <c r="J447" s="5" t="n">
-        <v>-7.383</v>
+        <v>7.383</v>
       </c>
       <c r="K447" s="5" t="n">
-        <v>-5.606</v>
+        <v>5.606</v>
       </c>
       <c r="L447" s="5" t="n">
-        <v>-5.48</v>
+        <v>5.48</v>
       </c>
       <c r="M447" t="inlineStr">
         <is>
@@ -54412,7 +54412,7 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
@@ -54431,10 +54431,10 @@
         </is>
       </c>
       <c r="H496" s="5" t="n">
-        <v>-5.026</v>
+        <v>5.026</v>
       </c>
       <c r="I496" s="5" t="n">
-        <v>-5.888</v>
+        <v>5.888</v>
       </c>
       <c r="J496" t="inlineStr">
         <is>
@@ -61612,7 +61612,7 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E573" s="5" t="n">

--- a/output/pdf_financials_xlsx/CRR.UN.xlsx
+++ b/output/pdf_financials_xlsx/CRR.UN.xlsx
@@ -1602,8 +1602,10 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>14.588</v>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C20" s="3" t="n">
         <v>10.748</v>
@@ -1684,7 +1686,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>0.649</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>0</v>
@@ -4566,19 +4568,19 @@
         <v>0</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.744</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>2.701</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>2.712</v>
       </c>
     </row>
     <row r="71">
@@ -4621,19 +4623,19 @@
         <v>0</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.744</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>3.503</v>
+        <v>4.444</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>12.527</v>
+        <v>15.228</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>2.712</v>
       </c>
     </row>
     <row r="72">
@@ -4841,19 +4843,19 @@
         <v>297.813</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>378.346</v>
+        <v>377.602</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>344.345</v>
+        <v>343.402</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>305.261</v>
+        <v>304.32</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>142.29</v>
+        <v>139.589</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>348.713</v>
+        <v>346.001</v>
       </c>
     </row>
     <row r="76">
@@ -5140,19 +5142,19 @@
         <v>0.1239520667572288</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.057031304229497</v>
+        <v>0.05754262932435673</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.1050077274741427</v>
+        <v>0.105517308461314</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.09850425792987719</v>
+        <v>0.09901995546696933</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.05193474675835606</v>
+        <v>0.05339038770384901</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>0.04926689081924238</v>
+        <v>0.05073880797505556</v>
       </c>
     </row>
     <row r="81">
@@ -10292,7 +10294,11 @@
           <t>Lease liabilities 21</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -12736,7 +12742,11 @@
           <t>Lease Liabilities 20</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -66244,7 +66254,11 @@
           <t>Income from discontinued operations (Note 22)</t>
         </is>
       </c>
-      <c r="D622" t="inlineStr"/>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E622" s="5" t="n">
         <v>0.649</v>
       </c>
